--- a/FROID_NR1_simulador.xlsx
+++ b/FROID_NR1_simulador.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Cenários" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Anonimato" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Alavancas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Concorrência" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -177,6 +178,19 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A20"/>
+  <dimension ref="A2:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -650,8 +664,39 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Concorrência</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sai VAZIA de propósito — nenhum valor foi estimado. Preencha com cotações reais e anote fonte e data: preço sem procedência não sustenta argumento em reunião.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Aceita cobrança mensal ou por campanha, e calcula sozinha anual, ano 1, custo por trabalhador e a diferença contra o FROID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Embaixo há a matriz de capacidades. Ela existe porque preço menor por escopo menor não é preço menor — é outro produto, e a diferença precisa aparecer na mesma tela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>O que esta planilha NÃO faz: não estima custo, não tem margem e não conhece preço de concorrente. É receita bruta. Enquanto o custo de operar uma campanha não estiver medido, ela mostra quanto entra — não quanto sobra.</t>
         </is>
@@ -2135,4 +2180,872 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Concorrência — preencher com cotações reais</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Nada aqui foi estimado. Preencha as células escuras com valores de propostas, tabelas públicas ou cotações recebidas — e anote a fonte e a data, porque preço sem procedência não sustenta argumento em reunião.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Referência FROID (vem da aba Receita)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Efetivo simulado</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>Receita!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Anual FROID (com desconto)</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>Receita!B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Implantação FROID</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>Receita!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ano 1 FROID (anual + implantação)</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>Receita!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Campanhas/ano FROID</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <f>Receita!B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cotações</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Preencha “Mensal recorrente” OU “Por campanha”, conforme o modelo da cotação. Se os dois estiverem preenchidos, o cálculo usa o mensal. “Campanhas/ano” em branco assume o mesmo número do FROID, para que a comparação seja sobre o mesmo ciclo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Modelo de cobrança</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Efetivo da cotação</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Implantação (única)</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>Mensal recorrente</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>Por campanha</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>Campanhas/ano incluídas</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>Prazo de entrega (dias)</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>Fonte e data da informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Comparação — calculada a partir do que for preenchido</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Anual do concorrente</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Ano 1 do concorrente</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Por trabalhador / ano</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>Por campanha</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>Ano 1 vs FROID (R$)</t>
+        </is>
+      </c>
+      <c r="G21" s="30" t="inlineStr">
+        <is>
+          <t>Ano 1 vs FROID (%)</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
+        <is>
+          <t>FROID está…</t>
+        </is>
+      </c>
+      <c r="I21" s="30" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25">
+        <f>IF(A13="","",A13)</f>
+        <v/>
+      </c>
+      <c r="B22" s="19">
+        <f>IF(AND(E13="",F13=""),"",IF(E13&lt;&gt;"",E13*12,F13*IF(G13="",$B$9,G13)))</f>
+        <v/>
+      </c>
+      <c r="C22" s="19">
+        <f>IF(B22="","",B22+IF(D13="",0,D13))</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>IF(OR(B22="",C13="",C13=0),"",B22/C13)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19">
+        <f>IF(B22="","",B22/IF(G13="",$B$9,G13))</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>IF(C22="","",$B$8-C22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="26">
+        <f>IF(OR(C22="",C22=0),"",$B$8/C22-1)</f>
+        <v/>
+      </c>
+      <c r="H22" s="27">
+        <f>IF(G22="","",IF(G22&gt;0.05,"mais caro",IF(G22&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25">
+        <f>IF(A14="","",A14)</f>
+        <v/>
+      </c>
+      <c r="B23" s="19">
+        <f>IF(AND(E14="",F14=""),"",IF(E14&lt;&gt;"",E14*12,F14*IF(G14="",$B$9,G14)))</f>
+        <v/>
+      </c>
+      <c r="C23" s="19">
+        <f>IF(B23="","",B23+IF(D14="",0,D14))</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>IF(OR(B23="",C14="",C14=0),"",B23/C14)</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>IF(B23="","",B23/IF(G14="",$B$9,G14))</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>IF(C23="","",$B$8-C23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="26">
+        <f>IF(OR(C23="",C23=0),"",$B$8/C23-1)</f>
+        <v/>
+      </c>
+      <c r="H23" s="27">
+        <f>IF(G23="","",IF(G23&gt;0.05,"mais caro",IF(G23&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25">
+        <f>IF(A15="","",A15)</f>
+        <v/>
+      </c>
+      <c r="B24" s="19">
+        <f>IF(AND(E15="",F15=""),"",IF(E15&lt;&gt;"",E15*12,F15*IF(G15="",$B$9,G15)))</f>
+        <v/>
+      </c>
+      <c r="C24" s="19">
+        <f>IF(B24="","",B24+IF(D15="",0,D15))</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>IF(OR(B24="",C15="",C15=0),"",B24/C15)</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>IF(B24="","",B24/IF(G15="",$B$9,G15))</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>IF(C24="","",$B$8-C24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="26">
+        <f>IF(OR(C24="",C24=0),"",$B$8/C24-1)</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>IF(G24="","",IF(G24&gt;0.05,"mais caro",IF(G24&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25">
+        <f>IF(A16="","",A16)</f>
+        <v/>
+      </c>
+      <c r="B25" s="19">
+        <f>IF(AND(E16="",F16=""),"",IF(E16&lt;&gt;"",E16*12,F16*IF(G16="",$B$9,G16)))</f>
+        <v/>
+      </c>
+      <c r="C25" s="19">
+        <f>IF(B25="","",B25+IF(D16="",0,D16))</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>IF(OR(B25="",C16="",C16=0),"",B25/C16)</f>
+        <v/>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(B25="","",B25/IF(G16="",$B$9,G16))</f>
+        <v/>
+      </c>
+      <c r="F25" s="19">
+        <f>IF(C25="","",$B$8-C25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="26">
+        <f>IF(OR(C25="",C25=0),"",$B$8/C25-1)</f>
+        <v/>
+      </c>
+      <c r="H25" s="27">
+        <f>IF(G25="","",IF(G25&gt;0.05,"mais caro",IF(G25&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25">
+        <f>IF(A17="","",A17)</f>
+        <v/>
+      </c>
+      <c r="B26" s="19">
+        <f>IF(AND(E17="",F17=""),"",IF(E17&lt;&gt;"",E17*12,F17*IF(G17="",$B$9,G17)))</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IF(B26="","",B26+IF(D17="",0,D17))</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>IF(OR(B26="",C17="",C17=0),"",B26/C17)</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IF(B26="","",B26/IF(G17="",$B$9,G17))</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IF(C26="","",$B$8-C26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="26">
+        <f>IF(OR(C26="",C26=0),"",$B$8/C26-1)</f>
+        <v/>
+      </c>
+      <c r="H26" s="27">
+        <f>IF(G26="","",IF(G26&gt;0.05,"mais caro",IF(G26&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25">
+        <f>IF(A18="","",A18)</f>
+        <v/>
+      </c>
+      <c r="B27" s="19">
+        <f>IF(AND(E18="",F18=""),"",IF(E18&lt;&gt;"",E18*12,F18*IF(G18="",$B$9,G18)))</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IF(B27="","",B27+IF(D18="",0,D18))</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>IF(OR(B27="",C18="",C18=0),"",B27/C18)</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IF(B27="","",B27/IF(G18="",$B$9,G18))</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IF(C27="","",$B$8-C27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="26">
+        <f>IF(OR(C27="",C27=0),"",$B$8/C27-1)</f>
+        <v/>
+      </c>
+      <c r="H27" s="27">
+        <f>IF(G27="","",IF(G27&gt;0.05,"mais caro",IF(G27&lt;-0.05,"mais barato","equivalente")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Cuidado ao comparar: quase nenhum concorrente entrega prova de eficácia antes/depois nem piso de anonimato. Preço menor por um escopo menor não é preço menor — é outro produto. A matriz abaixo existe para não deixar isso passar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  O que cada um entrega (preencher: sim / não / parcial)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Capacidade</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>FROID</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 1</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 2</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 3</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 4</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 5</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>Concorrente 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>(nome da cotação)</t>
+        </is>
+      </c>
+      <c r="C33" s="25">
+        <f>IF(A13="","",A13)</f>
+        <v/>
+      </c>
+      <c r="D33" s="25">
+        <f>IF(A14="","",A14)</f>
+        <v/>
+      </c>
+      <c r="E33" s="25">
+        <f>IF(A15="","",A15)</f>
+        <v/>
+      </c>
+      <c r="F33" s="25">
+        <f>IF(A16="","",A16)</f>
+        <v/>
+      </c>
+      <c r="G33" s="25">
+        <f>IF(A17="","",A17)</f>
+        <v/>
+      </c>
+      <c r="H33" s="25">
+        <f>IF(A18="","",A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>Inventário com os nove campos (1.5.7.3.2)</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>AEP psicossocial</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>Gradação por severidade × probabilidade (1.5.4.4.4)</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>Probabilidade desconta eficácia medida (1.5.4.4.5.3)</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>Prova de eficácia antes/depois, setor contra si mesmo</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>Medida ineficaz não reduz risco no papel (1.5.5.3.2.1)</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>Piso de anonimato por recorte</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>Resultado só após encerrar a campanha</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>Recusa abrir campanha sem canal de apoio</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>Critérios de gradação alinhados ao PGR da empresa</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>Guarda do histórico por 20 anos (1.5.7.3.3.1)</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>Painel próprio, sem planilha intermediária</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>Base legal declarada (obrigação legal, não consentimento)</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>Não entrega resposta individual a ninguém</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>A coluna FROID reflete o que está implementado no produto hoje. Se alguma linha deixar de ser verdade, corrija aqui antes de usar a matriz com um cliente.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/FROID_NR1_simulador.xlsx
+++ b/FROID_NR1_simulador.xlsx
@@ -1849,10 +1849,10 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="46" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>O menor departamento é quem manda. Um setor de 20 pessoas precisa de metade dele respondendo para existir no relatório — e é sobre esse setor que o cliente vai perguntar na reunião.</t>
+          <t>O menor departamento é quem manda: leia a coluna “Adesão mínima para publicar” de baixo para cima. Ela não é o piso dividido pelo efetivo — embute também a completude, porque resposta que não cobre metade das dimensões não conta. É por isso que a exigência do setor pequeno é maior do que a conta de cabeça sugere, e é sobre esse setor que o cliente vai perguntar na reunião.</t>
         </is>
       </c>
     </row>

--- a/FROID_NR1_simulador.xlsx
+++ b/FROID_NR1_simulador.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leia primeiro" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Receita" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cenários" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Anonimato" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Alavancas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Concorrência" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia primeiro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Receita" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anonimato" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alavancas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concorrência" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>100</v>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>300</v>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>1000</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>3</v>
+        <v>6.55</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B5" s="19">
         <f>Receita!$B$11+MEDIAN(0,A5,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A5-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A5-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A5-Receita!$C$14)*Receita!$B$15</f>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="B6" s="19">
         <f>Receita!$B$11+MEDIAN(0,A6,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A6-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A6-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A6-Receita!$C$14)*Receita!$B$15</f>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B7" s="19">
         <f>Receita!$B$11+MEDIAN(0,A7,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A7-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A7-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A7-Receita!$C$14)*Receita!$B$15</f>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="B8" s="19">
         <f>Receita!$B$11+MEDIAN(0,A8,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A8-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A8-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A8-Receita!$C$14)*Receita!$B$15</f>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19">
         <f>Receita!$B$11+MEDIAN(0,A9,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A9-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A9-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A9-Receita!$C$14)*Receita!$B$15</f>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="B10" s="19">
         <f>Receita!$B$11+MEDIAN(0,A10,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A10-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A10-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A10-Receita!$C$14)*Receita!$B$15</f>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="B11" s="19">
         <f>Receita!$B$11+MEDIAN(0,A11,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A11-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A11-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A11-Receita!$C$14)*Receita!$B$15</f>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>750</v>
+        <v>200</v>
       </c>
       <c r="B12" s="19">
         <f>Receita!$B$11+MEDIAN(0,A12,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A12-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A12-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A12-Receita!$C$14)*Receita!$B$15</f>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="B13" s="19">
         <f>Receita!$B$11+MEDIAN(0,A13,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A13-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A13-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A13-Receita!$C$14)*Receita!$B$15</f>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="B14" s="19">
         <f>Receita!$B$11+MEDIAN(0,A14,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A14-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A14-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A14-Receita!$C$14)*Receita!$B$15</f>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="B15" s="19">
         <f>Receita!$B$11+MEDIAN(0,A15,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A15-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A15-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A15-Receita!$C$14)*Receita!$B$15</f>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="B16" s="19">
         <f>Receita!$B$11+MEDIAN(0,A16,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A16-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A16-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A16-Receita!$C$14)*Receita!$B$15</f>
@@ -1508,8 +1508,83 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B17" s="19">
+        <f>Receita!$B$11+MEDIAN(0,A17,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A17-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A17-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A17-Receita!$C$14)*Receita!$B$15</f>
+        <v/>
+      </c>
+      <c r="C17" s="19">
+        <f>B17*12</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>C17/A17</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>B17/A17</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>IF(Receita!$B$35=0,"",C17/Receita!$B$35)</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B18" s="19">
+        <f>Receita!$B$11+MEDIAN(0,A18,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A18-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A18-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A18-Receita!$C$14)*Receita!$B$15</f>
+        <v/>
+      </c>
+      <c r="C18" s="19">
+        <f>B18*12</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>C18/A18</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>B18/A18</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>IF(Receita!$B$35=0,"",C18/Receita!$B$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B19" s="19">
+        <f>Receita!$B$11+MEDIAN(0,A19,Receita!$C$12)*Receita!$B$12+MEDIAN(0,A19-Receita!$C$12,Receita!$C$13-Receita!$C$12)*Receita!$B$13+MEDIAN(0,A19-Receita!$C$13,Receita!$C$14-Receita!$C$13)*Receita!$B$14+MAX(0,A19-Receita!$C$14)*Receita!$B$15</f>
+        <v/>
+      </c>
+      <c r="C19" s="19">
+        <f>B19*12</f>
+        <v/>
+      </c>
+      <c r="D19" s="16">
+        <f>C19/A19</f>
+        <v/>
+      </c>
+      <c r="E19" s="16">
+        <f>B19/A19</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>IF(Receita!$B$35=0,"",C19/Receita!$B$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Os efetivos de 50 e 75 estão aqui de propósito: abaixo de cerca de 75 a campanha não atinge o piso de anonimato e não produz resultado liberável. Ver a aba Anonimato antes de propor.</t>
         </is>
@@ -1575,7 +1650,7 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1973,19 +2048,19 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>3</v>
+        <v>6.55</v>
       </c>
       <c r="G7" s="18">
         <f>B7+MEDIAN(0,$B$4,Receita!$C$12)*C7+MEDIAN(0,$B$4-Receita!$C$12,Receita!$C$13-Receita!$C$12)*D7+MEDIAN(0,$B$4-Receita!$C$13,Receita!$C$14-Receita!$C$13)*E7+MAX(0,$B$4-Receita!$C$14)*F7</f>

--- a/FROID_NR1_simulador.xlsx
+++ b/FROID_NR1_simulador.xlsx
@@ -826,7 +826,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Base por unidade / mês</t>
+          <t>Base da plataforma, por estabelecimento / mês</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
